--- a/slow_control_functions.xlsx
+++ b/slow_control_functions.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dpfeiffe/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dpfeiffe/programming/VMM-software-RD51/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A2E55BB-275D-684A-90FA-CED3259A89C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08337BE7-C769-AE45-9635-7C1251F3E856}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="460" windowWidth="32800" windowHeight="20540" xr2:uid="{8ECCD076-F53F-F149-B310-CAA37E23BB36}"/>
+    <workbookView xWindow="800" yWindow="460" windowWidth="32800" windowHeight="20540" activeTab="1" xr2:uid="{8ECCD076-F53F-F149-B310-CAA37E23BB36}"/>
   </bookViews>
   <sheets>
     <sheet name="slow control" sheetId="7" r:id="rId1"/>
+    <sheet name="VMM3a settings" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="330">
   <si>
     <t>gen_reg_cfg2</t>
   </si>
@@ -235,13 +236,793 @@
   </si>
   <si>
     <t>init, read from 0x1787, write to 0x1777</t>
+  </si>
+  <si>
+    <t>ADDR</t>
+  </si>
+  <si>
+    <t>ADDR (hex)</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>VMM3a docu name</t>
+  </si>
+  <si>
+    <t>global SPI 0 / VMM3: global bank 2</t>
+  </si>
+  <si>
+    <t>00000000</t>
+  </si>
+  <si>
+    <t>[0,30]</t>
+  </si>
+  <si>
+    <t>[31,1]</t>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t>[31]</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>magic number on BCID</t>
+  </si>
+  <si>
+    <t>nskipm_i</t>
+  </si>
+  <si>
+    <t>global SPI 1 / VMM3: global bank 2</t>
+  </si>
+  <si>
+    <t>clocks when L0 core disabled</t>
+  </si>
+  <si>
+    <t>sL0cktest</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>[30]</t>
+  </si>
+  <si>
+    <t>invert DCK</t>
+  </si>
+  <si>
+    <t>sL0dckinv</t>
+  </si>
+  <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[29]</t>
+  </si>
+  <si>
+    <t>invert BCCLK</t>
+  </si>
+  <si>
+    <t>sL0ckinv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[3] </t>
+  </si>
+  <si>
+    <t>[28]</t>
+  </si>
+  <si>
+    <t>L0 core</t>
+  </si>
+  <si>
+    <t>sL0ena</t>
+  </si>
+  <si>
+    <t>[4,9]</t>
+  </si>
+  <si>
+    <t>[27,22]</t>
+  </si>
+  <si>
+    <t>Max hits per L0</t>
+  </si>
+  <si>
+    <t>truncate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[10,16] </t>
+  </si>
+  <si>
+    <t>[21,15]</t>
+  </si>
+  <si>
+    <t>L0 triggers to skip on overflow</t>
+  </si>
+  <si>
+    <t>nskip</t>
+  </si>
+  <si>
+    <t>[17,19]</t>
+  </si>
+  <si>
+    <t>[14,12]</t>
+  </si>
+  <si>
+    <t>size trigger window</t>
+  </si>
+  <si>
+    <t>window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[20,31] </t>
+  </si>
+  <si>
+    <t>[11,0]</t>
+  </si>
+  <si>
+    <t>Channel tagging BC rollover</t>
+  </si>
+  <si>
+    <t>rollover</t>
+  </si>
+  <si>
+    <t>global SPI 2 / VMM3: global bank 2</t>
+  </si>
+  <si>
+    <t>[0,11]</t>
+  </si>
+  <si>
+    <t>[31,20]</t>
+  </si>
+  <si>
+    <t>L0 BC offset</t>
+  </si>
+  <si>
+    <t>l0offset</t>
+  </si>
+  <si>
+    <t>[12,23]</t>
+  </si>
+  <si>
+    <t>[19,8]</t>
+  </si>
+  <si>
+    <t>Channel tagging BC offset</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>[24,31]</t>
+  </si>
+  <si>
+    <t>[7,0]</t>
+  </si>
+  <si>
+    <t>3 to 66</t>
+  </si>
+  <si>
+    <t>VMM channel 0 - 63</t>
+  </si>
+  <si>
+    <t>[0,7]</t>
+  </si>
+  <si>
+    <t>[31,24]</t>
+  </si>
+  <si>
+    <t>[8]</t>
+  </si>
+  <si>
+    <t>[23]</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>sc</t>
+  </si>
+  <si>
+    <t>[9]</t>
+  </si>
+  <si>
+    <t>[22]</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>sl</t>
+  </si>
+  <si>
+    <t>[10]</t>
+  </si>
+  <si>
+    <t>[21]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test pulse </t>
+  </si>
+  <si>
+    <t>st</t>
+  </si>
+  <si>
+    <t>[11]</t>
+  </si>
+  <si>
+    <t>[20]</t>
+  </si>
+  <si>
+    <t>STH</t>
+  </si>
+  <si>
+    <t>sth</t>
+  </si>
+  <si>
+    <t>[12]</t>
+  </si>
+  <si>
+    <t>[19]</t>
+  </si>
+  <si>
+    <t>masking</t>
+  </si>
+  <si>
+    <t>sm</t>
+  </si>
+  <si>
+    <t>[13]</t>
+  </si>
+  <si>
+    <t>[18]</t>
+  </si>
+  <si>
+    <t>SMX</t>
+  </si>
+  <si>
+    <t>smx</t>
+  </si>
+  <si>
+    <t>[14,18]</t>
+  </si>
+  <si>
+    <t>[17,13]</t>
+  </si>
+  <si>
+    <t>trim</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
+  <si>
+    <t>reversed</t>
+  </si>
+  <si>
+    <t>[19,23]</t>
+  </si>
+  <si>
+    <t>[12,8]</t>
+  </si>
+  <si>
+    <t>10 bit adc lsb</t>
+  </si>
+  <si>
+    <t>ADC0_10</t>
+  </si>
+  <si>
+    <t>[24,27]</t>
+  </si>
+  <si>
+    <t>[7,4]</t>
+  </si>
+  <si>
+    <t>8 bit adc lsb</t>
+  </si>
+  <si>
+    <t>ADC0_8</t>
+  </si>
+  <si>
+    <t>[28,30]</t>
+  </si>
+  <si>
+    <t>[3,1]</t>
+  </si>
+  <si>
+    <t>6 bit adc lsb</t>
+  </si>
+  <si>
+    <t>ADC0_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[31] </t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>global SPI 0 / VMM3: global bank 1</t>
+  </si>
+  <si>
+    <t>[0,3]</t>
+  </si>
+  <si>
+    <t>[31,18]</t>
+  </si>
+  <si>
+    <t>reserved</t>
+  </si>
+  <si>
+    <t>[4]</t>
+  </si>
+  <si>
+    <t>[27]</t>
+  </si>
+  <si>
+    <t>direct output IOs</t>
+  </si>
+  <si>
+    <t>slvs</t>
+  </si>
+  <si>
+    <t>[5]</t>
+  </si>
+  <si>
+    <t>[26]</t>
+  </si>
+  <si>
+    <t>skips ch 16-47</t>
+  </si>
+  <si>
+    <t>s32</t>
+  </si>
+  <si>
+    <t>[6]</t>
+  </si>
+  <si>
+    <t>[25]</t>
+  </si>
+  <si>
+    <t>auto-reset at end ramp</t>
+  </si>
+  <si>
+    <t>stcr</t>
+  </si>
+  <si>
+    <t>[7]</t>
+  </si>
+  <si>
+    <t>[24]</t>
+  </si>
+  <si>
+    <t>ART flag synchronization</t>
+  </si>
+  <si>
+    <t>ssart</t>
+  </si>
+  <si>
+    <t>fast recovery from high charge</t>
+  </si>
+  <si>
+    <t>srec</t>
+  </si>
+  <si>
+    <t>mild tail cancellation</t>
+  </si>
+  <si>
+    <t>stlc</t>
+  </si>
+  <si>
+    <t>bipolar shape</t>
+  </si>
+  <si>
+    <t>sbip</t>
+  </si>
+  <si>
+    <t>timing ramp at threshold</t>
+  </si>
+  <si>
+    <t>srat</t>
+  </si>
+  <si>
+    <t>fast reset at 6-b completion</t>
+  </si>
+  <si>
+    <t>sfrst</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on ckbc</t>
+  </si>
+  <si>
+    <t>slvsbc</t>
+  </si>
+  <si>
+    <t>[14]</t>
+  </si>
+  <si>
+    <t>[17]</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on cktp</t>
+  </si>
+  <si>
+    <t>slvstp</t>
+  </si>
+  <si>
+    <t>[15]</t>
+  </si>
+  <si>
+    <t>[16]</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on cktk</t>
+  </si>
+  <si>
+    <t>slvstk</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on ckdt</t>
+  </si>
+  <si>
+    <t>slvsdt</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on ckart</t>
+  </si>
+  <si>
+    <t>slvsart</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on cktki</t>
+  </si>
+  <si>
+    <t>slvstki</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on ckena</t>
+  </si>
+  <si>
+    <t>slvsena</t>
+  </si>
+  <si>
+    <t>slvs 100 Ohm termination on ck6bslvs 100 Ohm termination on ck6b</t>
+  </si>
+  <si>
+    <t>slvs6b</t>
+  </si>
+  <si>
+    <t>mixed signal functions</t>
+  </si>
+  <si>
+    <t>sL0enaV</t>
+  </si>
+  <si>
+    <t>[22,29]</t>
+  </si>
+  <si>
+    <t>[9,2]</t>
+  </si>
+  <si>
+    <t>reset 1</t>
+  </si>
+  <si>
+    <t>reset1</t>
+  </si>
+  <si>
+    <t>reset 2</t>
+  </si>
+  <si>
+    <t>reset2</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>global SPI 1 / VMM3: global bank 1</t>
+  </si>
+  <si>
+    <t>292c0140</t>
+  </si>
+  <si>
+    <t>lowest 6  bits of 330: 001010</t>
+  </si>
+  <si>
+    <t>[0,5]</t>
+  </si>
+  <si>
+    <t>[31,26]</t>
+  </si>
+  <si>
+    <t>threshold DAC lowest 6 bits</t>
+  </si>
+  <si>
+    <t>sdt</t>
+  </si>
+  <si>
+    <t>300: 0100101100</t>
+  </si>
+  <si>
+    <t>[6,15]</t>
+  </si>
+  <si>
+    <t>[25,16]</t>
+  </si>
+  <si>
+    <t>pulse DAC</t>
+  </si>
+  <si>
+    <t>sdp_2</t>
+  </si>
+  <si>
+    <t>[16,17]</t>
+  </si>
+  <si>
+    <t>[15,14]</t>
+  </si>
+  <si>
+    <t>10bit ADC</t>
+  </si>
+  <si>
+    <t>convtime_10</t>
+  </si>
+  <si>
+    <t>[18,19]</t>
+  </si>
+  <si>
+    <t>[13,12]</t>
+  </si>
+  <si>
+    <t>8bit ADC</t>
+  </si>
+  <si>
+    <t>convtime_8</t>
+  </si>
+  <si>
+    <t>[20,22]</t>
+  </si>
+  <si>
+    <t>[11,9]</t>
+  </si>
+  <si>
+    <t>6bit</t>
+  </si>
+  <si>
+    <t>convtime_6</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>8-bit enable</t>
+  </si>
+  <si>
+    <t>s8b</t>
+  </si>
+  <si>
+    <t>6-bit enable</t>
+  </si>
+  <si>
+    <t>s6b</t>
+  </si>
+  <si>
+    <t>ADC enable</t>
+  </si>
+  <si>
+    <t>s10b</t>
+  </si>
+  <si>
+    <t>dual clock serialized</t>
+  </si>
+  <si>
+    <t>sdcks</t>
+  </si>
+  <si>
+    <t>dual clock ART</t>
+  </si>
+  <si>
+    <t>sdcka</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>dual clock 6-bit</t>
+  </si>
+  <si>
+    <t>sdck6b</t>
+  </si>
+  <si>
+    <t>analog tri-states</t>
+  </si>
+  <si>
+    <t>sdrv</t>
+  </si>
+  <si>
+    <t>timing out 2</t>
+  </si>
+  <si>
+    <t>stpp</t>
+  </si>
+  <si>
+    <t>bit 0 left - bit 31 right</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>global SPI 2 / VMM3: global bank 1</t>
+  </si>
+  <si>
+    <t>0020dc15</t>
+  </si>
+  <si>
+    <t>polarity, sp</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>disable at peak, sdp</t>
+  </si>
+  <si>
+    <t>sdp</t>
+  </si>
+  <si>
+    <t>analog monitor to pdo, sbmx</t>
+  </si>
+  <si>
+    <t>sbmx</t>
+  </si>
+  <si>
+    <t>tdo buffer</t>
+  </si>
+  <si>
+    <t>sbft</t>
+  </si>
+  <si>
+    <t>pdo buffer</t>
+  </si>
+  <si>
+    <t>sbfp</t>
+  </si>
+  <si>
+    <t>mo buffer</t>
+  </si>
+  <si>
+    <t>sbfm</t>
+  </si>
+  <si>
+    <t>leakage current</t>
+  </si>
+  <si>
+    <t>slg</t>
+  </si>
+  <si>
+    <t>[7,12]</t>
+  </si>
+  <si>
+    <t>[24,19]</t>
+  </si>
+  <si>
+    <t>channel to monitor</t>
+  </si>
+  <si>
+    <t>monitoring</t>
+  </si>
+  <si>
+    <t>multiplexer</t>
+  </si>
+  <si>
+    <t>scmx</t>
+  </si>
+  <si>
+    <t>ART enable</t>
+  </si>
+  <si>
+    <t>sfa</t>
+  </si>
+  <si>
+    <t>ART mode</t>
+  </si>
+  <si>
+    <t>sfam</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>peak_time</t>
+  </si>
+  <si>
+    <t>peaktime</t>
+  </si>
+  <si>
+    <t>double leakage (doubles the leakage current)</t>
+  </si>
+  <si>
+    <t>sfm</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>[19,21]</t>
+  </si>
+  <si>
+    <t>[12,10]</t>
+  </si>
+  <si>
+    <t>gain</t>
+  </si>
+  <si>
+    <t>neighbor trigger</t>
+  </si>
+  <si>
+    <t>sng</t>
+  </si>
+  <si>
+    <t>direct outputs settings</t>
+  </si>
+  <si>
+    <t>stot</t>
+  </si>
+  <si>
+    <t>direct timing</t>
+  </si>
+  <si>
+    <t>sttt</t>
+  </si>
+  <si>
+    <t>sub-hysteresis</t>
+  </si>
+  <si>
+    <t>ssh</t>
+  </si>
+  <si>
+    <t>[26,27]</t>
+  </si>
+  <si>
+    <t>[5,4]</t>
+  </si>
+  <si>
+    <t>TAC slope adjustment</t>
+  </si>
+  <si>
+    <t>stc</t>
+  </si>
+  <si>
+    <t>highest 4 bits of 330</t>
+  </si>
+  <si>
+    <t>[28,31]</t>
+  </si>
+  <si>
+    <t>[3,0]</t>
+  </si>
+  <si>
+    <t>threshold DAC highest 4 bits</t>
+  </si>
+  <si>
+    <t>sc string position (left most position is 0)</t>
+  </si>
+  <si>
+    <t>bits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -265,6 +1046,34 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -305,7 +1114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -430,11 +1239,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -478,9 +1303,41 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{E563DCB9-05B5-FE48-8441-EEBA5B82760A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1297,4 +2154,1361 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A489271B-B53B-D14B-8A4C-A360ABE07DCD}">
+  <dimension ref="A1:I102"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" style="55" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.1640625" style="51" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="57.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.1640625" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="47"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>328</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="45" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="D2" s="50"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="47">
+        <v>0</v>
+      </c>
+      <c r="B3" s="53">
+        <v>0</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E4" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E5" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D7" s="50"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="47">
+        <v>1</v>
+      </c>
+      <c r="B8" s="53">
+        <v>1</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E9" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E10" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E11" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E12" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E13" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E14" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E15" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E16" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D18" s="50"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="47">
+        <v>2</v>
+      </c>
+      <c r="B19" s="53">
+        <v>2</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E20" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E21" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E22" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D24" s="50"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="55"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E26" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E27" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E28" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E29" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E30" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E31" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E32" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E33" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E34" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="G34" s="59" t="s">
+        <v>162</v>
+      </c>
+      <c r="H34" s="59" t="s">
+        <v>163</v>
+      </c>
+      <c r="I34" s="59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E35" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="G35" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="H35" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="I35" s="59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E36" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="G36" s="59" t="s">
+        <v>170</v>
+      </c>
+      <c r="H36" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="I36" s="59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E37" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D39" s="50"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="47">
+        <v>67</v>
+      </c>
+      <c r="B40" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="C40" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="60" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="61"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="47" t="s">
+        <v>177</v>
+      </c>
+      <c r="H41" s="47"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E42" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="F42" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="G42" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="H42" s="47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E43" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="F43" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="G43" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="H43" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E44" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="F44" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E45" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="F45" s="52" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E46" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="F46" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="G46" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="H46" s="47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E47" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E48" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="F48" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="H48" s="47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E49" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="F49" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="H49" s="47" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E50" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="52" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="H50" s="47" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="51" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E51" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="F51" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="G51" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="H51" s="47" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="52" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E52" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="F52" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="G52" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="H52" s="47" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="53" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E53" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="F53" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="G53" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="H53" s="47" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E54" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="F54" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="G54" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="H54" s="47" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="55" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E55" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="F55" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="G55" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="H55" s="47" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E56" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="F56" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="G56" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="H56" s="47" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E57" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="F57" s="52" t="s">
+        <v>147</v>
+      </c>
+      <c r="G57" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="H57" s="47" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="58" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E58" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="F58" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="G58" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="H58" s="47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="59" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E59" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="G59" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="H59" s="47" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="60" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E60" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="F60" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="G60" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="H60" s="47" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E61" s="62" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="G61" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="H61" s="47" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="62" spans="5:8" x14ac:dyDescent="0.2">
+      <c r="E62" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="H62" s="47" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="47">
+        <v>68</v>
+      </c>
+      <c r="B65" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="D65" s="54" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D66" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="F66" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="G66" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="H66" s="47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D67" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="E67" s="51" t="s">
+        <v>241</v>
+      </c>
+      <c r="F67" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C68" s="64"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="F68" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="G68" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="H68" s="47" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C69" s="64"/>
+      <c r="D69" s="65"/>
+      <c r="E69" s="51" t="s">
+        <v>249</v>
+      </c>
+      <c r="F69" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="G69" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="H69" s="47" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C70" s="64"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="51" t="s">
+        <v>253</v>
+      </c>
+      <c r="F70" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="G70" s="47" t="s">
+        <v>255</v>
+      </c>
+      <c r="H70" s="47" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C71" s="64"/>
+      <c r="D71" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="E71" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F71" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="G71" s="47" t="s">
+        <v>258</v>
+      </c>
+      <c r="H71" s="47" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C72" s="64"/>
+      <c r="D72" s="65"/>
+      <c r="E72" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="F72" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="G72" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="H72" s="47" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C73" s="64"/>
+      <c r="D73" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="E73" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="F73" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G73" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="H73" s="47" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C74" s="64"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="F74" s="52" t="s">
+        <v>182</v>
+      </c>
+      <c r="G74" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="H74" s="47" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C75" s="64"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="F75" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="G75" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="H75" s="47" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C76" s="64"/>
+      <c r="D76" s="65"/>
+      <c r="E76" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="F76" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="G76" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="H76" s="47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C77" s="64"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="F77" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G77" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="H77" s="47" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C78" s="64"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="F78" s="52" t="s">
+        <v>88</v>
+      </c>
+      <c r="G78" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="H78" s="47" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C79" s="64"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F79" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D81" s="55" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="47">
+        <v>69</v>
+      </c>
+      <c r="B82" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="C82" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="D82" s="54" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E83" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="F83" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="G83" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="H83" s="47" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E84" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="F84" s="52" t="s">
+        <v>89</v>
+      </c>
+      <c r="G84" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="H84" s="47" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E85" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F85" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="G85" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="H85" s="47" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E86" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="F86" s="52" t="s">
+        <v>97</v>
+      </c>
+      <c r="G86" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="H86" s="47" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E87" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="F87" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="G87" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="H87" s="47" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E88" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="F88" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="G88" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="H88" s="47" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E89" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="F89" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="G89" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="H89" s="47" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E90" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="F90" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="G90" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="H90" s="47" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E91" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="F91" s="52" t="s">
+        <v>152</v>
+      </c>
+      <c r="G91" s="47" t="s">
+        <v>297</v>
+      </c>
+      <c r="H91" s="47" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E92" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="F92" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="G92" s="47" t="s">
+        <v>299</v>
+      </c>
+      <c r="H92" s="47" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E93" s="51" t="s">
+        <v>210</v>
+      </c>
+      <c r="F93" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="G93" s="47" t="s">
+        <v>301</v>
+      </c>
+      <c r="H93" s="47" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D94" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="E94" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="F94" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="G94" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="H94" s="47" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E95" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="F95" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="G95" s="47" t="s">
+        <v>306</v>
+      </c>
+      <c r="H95" s="47" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D96" s="55" t="s">
+        <v>308</v>
+      </c>
+      <c r="E96" s="51" t="s">
+        <v>309</v>
+      </c>
+      <c r="F96" s="52" t="s">
+        <v>310</v>
+      </c>
+      <c r="G96" s="47" t="s">
+        <v>311</v>
+      </c>
+      <c r="H96" s="47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="97" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="E97" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="F97" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="G97" s="47" t="s">
+        <v>312</v>
+      </c>
+      <c r="H97" s="47" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="E98" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F98" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="G98" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="H98" s="47" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="E99" s="51" t="s">
+        <v>191</v>
+      </c>
+      <c r="F99" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="G99" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="H99" s="47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="E100" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="F100" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G100" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="H100" s="47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D101" s="55" t="s">
+        <v>257</v>
+      </c>
+      <c r="E101" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="F101" s="52" t="s">
+        <v>321</v>
+      </c>
+      <c r="G101" s="47" t="s">
+        <v>322</v>
+      </c>
+      <c r="H101" s="47" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="102" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D102" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="E102" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="F102" s="52" t="s">
+        <v>326</v>
+      </c>
+      <c r="G102" s="47" t="s">
+        <v>327</v>
+      </c>
+      <c r="H102" s="47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>